--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121290845</v>
+        <v>121317429</v>
       </c>
       <c r="B2" t="n">
-        <v>90705</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760289</v>
+        <v>760542</v>
       </c>
       <c r="R2" t="n">
-        <v>7122383</v>
+        <v>7122063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,29 +768,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121317432</v>
+        <v>121290845</v>
       </c>
       <c r="B3" t="n">
-        <v>57364</v>
+        <v>90715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760608</v>
+        <v>760289</v>
       </c>
       <c r="R3" t="n">
-        <v>7122166</v>
+        <v>7122383</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,39 +867,35 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121317429</v>
+        <v>121317432</v>
       </c>
       <c r="B4" t="n">
-        <v>56563</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,20 +904,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -922,20 +926,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760542</v>
+        <v>760608</v>
       </c>
       <c r="R4" t="n">
-        <v>7122063</v>
+        <v>7122166</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,7 +1002,7 @@
         <v>121291222</v>
       </c>
       <c r="B5" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>121340153</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121317429</v>
+        <v>121290845</v>
       </c>
       <c r="B2" t="n">
-        <v>56566</v>
+        <v>90715</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760542</v>
+        <v>760289</v>
       </c>
       <c r="R2" t="n">
-        <v>7122063</v>
+        <v>7122383</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121290845</v>
+        <v>121317432</v>
       </c>
       <c r="B3" t="n">
-        <v>90715</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,37 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760289</v>
+        <v>760608</v>
       </c>
       <c r="R3" t="n">
-        <v>7122383</v>
+        <v>7122166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,35 +859,39 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121317432</v>
+        <v>121317429</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>56566</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,20 +900,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -926,16 +922,20 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760608</v>
+        <v>760542</v>
       </c>
       <c r="R4" t="n">
-        <v>7122166</v>
+        <v>7122063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +962,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121290845</v>
       </c>
       <c r="B2" t="n">
-        <v>90715</v>
+        <v>90727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -888,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121317429</v>
+        <v>121291222</v>
       </c>
       <c r="B4" t="n">
-        <v>56566</v>
+        <v>57720</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,16 +904,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,21 +921,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760542</v>
+        <v>760585</v>
       </c>
       <c r="R4" t="n">
-        <v>7122063</v>
+        <v>7122118</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,22 +990,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291222</v>
+        <v>121317429</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>56566</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,16 +1018,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,29 +1035,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760585</v>
+        <v>760542</v>
       </c>
       <c r="R5" t="n">
-        <v>7122118</v>
+        <v>7122063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,12 +1076,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         <v>121340153</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121290845</v>
+        <v>121317429</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
+        <v>56566</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760289</v>
+        <v>760542</v>
       </c>
       <c r="R2" t="n">
-        <v>7122383</v>
+        <v>7122063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,19 +768,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -1002,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121317429</v>
+        <v>121290845</v>
       </c>
       <c r="B5" t="n">
-        <v>56566</v>
+        <v>90728</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,42 +1019,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760542</v>
+        <v>760289</v>
       </c>
       <c r="R5" t="n">
-        <v>7122063</v>
+        <v>7122383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1080,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,18 +1094,19 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121317429</v>
+        <v>121291222</v>
       </c>
       <c r="B2" t="n">
-        <v>56566</v>
+        <v>57723</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,21 +708,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760542</v>
+        <v>760585</v>
       </c>
       <c r="R2" t="n">
-        <v>7122063</v>
+        <v>7122118</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +757,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,22 +777,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121317432</v>
+        <v>121317429</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>56569</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -820,16 +823,20 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760608</v>
+        <v>760542</v>
       </c>
       <c r="R3" t="n">
-        <v>7122166</v>
+        <v>7122063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -856,17 +863,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291222</v>
+        <v>121290845</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,39 +912,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760585</v>
+        <v>760289</v>
       </c>
       <c r="R4" t="n">
-        <v>7122118</v>
+        <v>7122383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,6 +987,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121290845</v>
+        <v>121317432</v>
       </c>
       <c r="B5" t="n">
-        <v>90728</v>
+        <v>57370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,37 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760289</v>
+        <v>760608</v>
       </c>
       <c r="R5" t="n">
-        <v>7122383</v>
+        <v>7122166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,25 +1084,29 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         <v>121340153</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121317429</v>
+        <v>121317432</v>
       </c>
       <c r="B3" t="n">
-        <v>56569</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,20 +823,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760542</v>
+        <v>760608</v>
       </c>
       <c r="R3" t="n">
-        <v>7122063</v>
+        <v>7122166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,17 +859,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121290845</v>
+        <v>121317429</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>56569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,41 +908,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760289</v>
+        <v>760542</v>
       </c>
       <c r="R4" t="n">
-        <v>7122383</v>
+        <v>7122063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -973,12 +970,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,29 +989,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121317432</v>
+        <v>121290845</v>
       </c>
       <c r="B5" t="n">
-        <v>57370</v>
+        <v>90731</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,34 +1023,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760608</v>
+        <v>760289</v>
       </c>
       <c r="R5" t="n">
-        <v>7122166</v>
+        <v>7122383</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,29 +1088,25 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291222</v>
+        <v>121317429</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>56570</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,29 +708,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760585</v>
+        <v>760542</v>
       </c>
       <c r="R2" t="n">
-        <v>7122118</v>
+        <v>7122063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,12 +774,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -792,7 +789,7 @@
         <v>121317432</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -896,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121317429</v>
+        <v>121290845</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>90737</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,42 +905,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760542</v>
+        <v>760289</v>
       </c>
       <c r="R4" t="n">
-        <v>7122063</v>
+        <v>7122383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,17 +966,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,28 +980,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121290845</v>
+        <v>121291222</v>
       </c>
       <c r="B5" t="n">
-        <v>90731</v>
+        <v>57724</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,30 +1011,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760289</v>
+        <v>760585</v>
       </c>
       <c r="R5" t="n">
-        <v>7122383</v>
+        <v>7122118</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1095,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>121340153</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,6 +1217,516 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121569151</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79226</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>760287</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7122048</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121569150</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78345</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>760290</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7122046</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121569152</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98021</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>760302</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7122172</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121569154</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98021</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>760429</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7122253</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121569153</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>760382</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7122140</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121317429</v>
+        <v>121317432</v>
       </c>
       <c r="B2" t="n">
-        <v>56570</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,20 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760542</v>
+        <v>760608</v>
       </c>
       <c r="R2" t="n">
-        <v>7122063</v>
+        <v>7122166</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121317432</v>
+        <v>121291222</v>
       </c>
       <c r="B3" t="n">
-        <v>57371</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,20 +794,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,17 +815,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760608</v>
+        <v>760585</v>
       </c>
       <c r="R3" t="n">
-        <v>7122166</v>
+        <v>7122118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,11 +872,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -881,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -896,7 +899,7 @@
         <v>121290845</v>
       </c>
       <c r="B4" t="n">
-        <v>90737</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121291222</v>
+        <v>121317429</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>56571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,16 +1018,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1032,29 +1035,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760585</v>
+        <v>760542</v>
       </c>
       <c r="R5" t="n">
-        <v>7122118</v>
+        <v>7122063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,12 +1076,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1116,7 +1116,7 @@
         <v>121340153</v>
       </c>
       <c r="B6" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>121569151</v>
       </c>
       <c r="B7" t="n">
-        <v>79226</v>
+        <v>79227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569150</v>
+        <v>121569153</v>
       </c>
       <c r="B8" t="n">
-        <v>78345</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760290</v>
+        <v>760382</v>
       </c>
       <c r="R8" t="n">
-        <v>7122046</v>
+        <v>7122140</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569152</v>
+        <v>121569154</v>
       </c>
       <c r="B9" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760302</v>
+        <v>760429</v>
       </c>
       <c r="R9" t="n">
-        <v>7122172</v>
+        <v>7122253</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569154</v>
+        <v>121569152</v>
       </c>
       <c r="B10" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760429</v>
+        <v>760302</v>
       </c>
       <c r="R10" t="n">
-        <v>7122253</v>
+        <v>7122172</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569153</v>
+        <v>121569150</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>78346</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760382</v>
+        <v>760290</v>
       </c>
       <c r="R11" t="n">
-        <v>7122140</v>
+        <v>7122046</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121317432</v>
+        <v>121291222</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>57725</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,17 +708,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760608</v>
+        <v>760585</v>
       </c>
       <c r="R2" t="n">
-        <v>7122166</v>
+        <v>7122118</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,11 +765,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -770,22 +777,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291222</v>
+        <v>121317432</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -815,29 +822,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760585</v>
+        <v>760608</v>
       </c>
       <c r="R3" t="n">
-        <v>7122118</v>
+        <v>7122166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,6 +867,11 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -884,12 +884,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569151</v>
+        <v>121569154</v>
       </c>
       <c r="B7" t="n">
-        <v>79227</v>
+        <v>98022</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760287</v>
+        <v>760429</v>
       </c>
       <c r="R7" t="n">
-        <v>7122048</v>
+        <v>7122253</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569153</v>
+        <v>121569150</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78346</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760382</v>
+        <v>760290</v>
       </c>
       <c r="R8" t="n">
-        <v>7122140</v>
+        <v>7122046</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569154</v>
+        <v>121569153</v>
       </c>
       <c r="B9" t="n">
-        <v>98022</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,25 +1435,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760429</v>
+        <v>760382</v>
       </c>
       <c r="R9" t="n">
-        <v>7122253</v>
+        <v>7122140</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569152</v>
+        <v>121569151</v>
       </c>
       <c r="B10" t="n">
-        <v>98022</v>
+        <v>79227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760302</v>
+        <v>760287</v>
       </c>
       <c r="R10" t="n">
-        <v>7122172</v>
+        <v>7122048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569150</v>
+        <v>121569152</v>
       </c>
       <c r="B11" t="n">
-        <v>78346</v>
+        <v>98022</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760290</v>
+        <v>760302</v>
       </c>
       <c r="R11" t="n">
-        <v>7122046</v>
+        <v>7122172</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121291222</v>
+        <v>121317429</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>56571</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,29 +708,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760585</v>
+        <v>760542</v>
       </c>
       <c r="R2" t="n">
-        <v>7122118</v>
+        <v>7122063</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,22 +774,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121317432</v>
+        <v>121291222</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57725</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,20 +798,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -822,17 +819,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760608</v>
+        <v>760585</v>
       </c>
       <c r="R3" t="n">
-        <v>7122166</v>
+        <v>7122118</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,11 +876,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -884,12 +888,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1002,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121317429</v>
+        <v>121317432</v>
       </c>
       <c r="B5" t="n">
-        <v>56571</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,20 +1018,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1036,20 +1040,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760542</v>
+        <v>760608</v>
       </c>
       <c r="R5" t="n">
-        <v>7122063</v>
+        <v>7122166</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>6 st</t>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569154</v>
+        <v>121569150</v>
       </c>
       <c r="B7" t="n">
-        <v>98022</v>
+        <v>78346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760429</v>
+        <v>760290</v>
       </c>
       <c r="R7" t="n">
-        <v>7122253</v>
+        <v>7122046</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569150</v>
+        <v>121569152</v>
       </c>
       <c r="B8" t="n">
-        <v>78346</v>
+        <v>98022</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760290</v>
+        <v>760302</v>
       </c>
       <c r="R8" t="n">
-        <v>7122046</v>
+        <v>7122172</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569151</v>
+        <v>121569154</v>
       </c>
       <c r="B10" t="n">
-        <v>79227</v>
+        <v>98022</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760287</v>
+        <v>760429</v>
       </c>
       <c r="R10" t="n">
-        <v>7122048</v>
+        <v>7122253</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569152</v>
+        <v>121569151</v>
       </c>
       <c r="B11" t="n">
-        <v>98022</v>
+        <v>79227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760302</v>
+        <v>760287</v>
       </c>
       <c r="R11" t="n">
-        <v>7122172</v>
+        <v>7122048</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121317429</v>
+        <v>121290845</v>
       </c>
       <c r="B2" t="n">
-        <v>56571</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760542</v>
+        <v>760289</v>
       </c>
       <c r="R2" t="n">
-        <v>7122063</v>
+        <v>7122383</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,17 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121291222</v>
+        <v>121317429</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>56571</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,29 +814,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760585</v>
+        <v>760542</v>
       </c>
       <c r="R3" t="n">
-        <v>7122118</v>
+        <v>7122063</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,12 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,22 +880,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121290845</v>
+        <v>121317432</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,37 +908,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760289</v>
+        <v>760608</v>
       </c>
       <c r="R4" t="n">
-        <v>7122383</v>
+        <v>7122166</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,35 +970,39 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121317432</v>
+        <v>121291222</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57725</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,20 +1011,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1039,17 +1032,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760608</v>
+        <v>760585</v>
       </c>
       <c r="R5" t="n">
-        <v>7122166</v>
+        <v>7122118</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,11 +1089,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1101,12 +1101,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569150</v>
+        <v>121569151</v>
       </c>
       <c r="B7" t="n">
-        <v>78346</v>
+        <v>79227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760290</v>
+        <v>760287</v>
       </c>
       <c r="R7" t="n">
-        <v>7122046</v>
+        <v>7122048</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569152</v>
+        <v>121569153</v>
       </c>
       <c r="B8" t="n">
-        <v>98022</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760302</v>
+        <v>760382</v>
       </c>
       <c r="R8" t="n">
-        <v>7122172</v>
+        <v>7122140</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569153</v>
+        <v>121569154</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>98022</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,25 +1435,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760382</v>
+        <v>760429</v>
       </c>
       <c r="R9" t="n">
-        <v>7122140</v>
+        <v>7122253</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569154</v>
+        <v>121569150</v>
       </c>
       <c r="B10" t="n">
-        <v>98022</v>
+        <v>78346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760429</v>
+        <v>760290</v>
       </c>
       <c r="R10" t="n">
-        <v>7122253</v>
+        <v>7122046</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569151</v>
+        <v>121569152</v>
       </c>
       <c r="B11" t="n">
-        <v>79227</v>
+        <v>98022</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760287</v>
+        <v>760302</v>
       </c>
       <c r="R11" t="n">
-        <v>7122048</v>
+        <v>7122172</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569152</v>
+        <v>121569154</v>
       </c>
       <c r="B7" t="n">
         <v>98030</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760302</v>
+        <v>760429</v>
       </c>
       <c r="R7" t="n">
-        <v>7122172</v>
+        <v>7122253</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569150</v>
+        <v>121569151</v>
       </c>
       <c r="B8" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760290</v>
+        <v>760287</v>
       </c>
       <c r="R8" t="n">
-        <v>7122046</v>
+        <v>7122048</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569151</v>
+        <v>121569153</v>
       </c>
       <c r="B9" t="n">
-        <v>79234</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760287</v>
+        <v>760382</v>
       </c>
       <c r="R9" t="n">
-        <v>7122048</v>
+        <v>7122140</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569153</v>
+        <v>121569150</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>78353</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760382</v>
+        <v>760290</v>
       </c>
       <c r="R10" t="n">
-        <v>7122140</v>
+        <v>7122046</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,7 +1627,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569154</v>
+        <v>121569152</v>
       </c>
       <c r="B11" t="n">
         <v>98030</v>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760429</v>
+        <v>760302</v>
       </c>
       <c r="R11" t="n">
-        <v>7122253</v>
+        <v>7122172</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569154</v>
+        <v>121569150</v>
       </c>
       <c r="B7" t="n">
-        <v>98030</v>
+        <v>78353</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760429</v>
+        <v>760290</v>
       </c>
       <c r="R7" t="n">
-        <v>7122253</v>
+        <v>7122046</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569151</v>
+        <v>121569154</v>
       </c>
       <c r="B8" t="n">
-        <v>79234</v>
+        <v>98030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760287</v>
+        <v>760429</v>
       </c>
       <c r="R8" t="n">
-        <v>7122048</v>
+        <v>7122253</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569150</v>
+        <v>121569152</v>
       </c>
       <c r="B10" t="n">
-        <v>78353</v>
+        <v>98030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760290</v>
+        <v>760302</v>
       </c>
       <c r="R10" t="n">
-        <v>7122046</v>
+        <v>7122172</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569152</v>
+        <v>121569151</v>
       </c>
       <c r="B11" t="n">
-        <v>98030</v>
+        <v>79234</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760302</v>
+        <v>760287</v>
       </c>
       <c r="R11" t="n">
-        <v>7122172</v>
+        <v>7122048</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -1321,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569154</v>
+        <v>121569152</v>
       </c>
       <c r="B8" t="n">
         <v>98030</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760429</v>
+        <v>760302</v>
       </c>
       <c r="R8" t="n">
-        <v>7122253</v>
+        <v>7122172</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569153</v>
+        <v>121569151</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760382</v>
+        <v>760287</v>
       </c>
       <c r="R9" t="n">
-        <v>7122140</v>
+        <v>7122048</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569152</v>
+        <v>121569153</v>
       </c>
       <c r="B10" t="n">
-        <v>98030</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1537,25 +1537,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760302</v>
+        <v>760382</v>
       </c>
       <c r="R10" t="n">
-        <v>7122172</v>
+        <v>7122140</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569151</v>
+        <v>121569154</v>
       </c>
       <c r="B11" t="n">
-        <v>79234</v>
+        <v>98030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760287</v>
+        <v>760429</v>
       </c>
       <c r="R11" t="n">
-        <v>7122048</v>
+        <v>7122253</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569150</v>
+        <v>121569151</v>
       </c>
       <c r="B7" t="n">
-        <v>78353</v>
+        <v>79234</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,21 +1235,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760290</v>
+        <v>760287</v>
       </c>
       <c r="R7" t="n">
-        <v>7122046</v>
+        <v>7122048</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569151</v>
+        <v>121569150</v>
       </c>
       <c r="B9" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1439,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760287</v>
+        <v>760290</v>
       </c>
       <c r="R9" t="n">
-        <v>7122048</v>
+        <v>7122046</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569151</v>
+        <v>121569152</v>
       </c>
       <c r="B7" t="n">
-        <v>79234</v>
+        <v>98030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760287</v>
+        <v>760302</v>
       </c>
       <c r="R7" t="n">
-        <v>7122048</v>
+        <v>7122172</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569152</v>
+        <v>121569154</v>
       </c>
       <c r="B8" t="n">
         <v>98030</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760302</v>
+        <v>760429</v>
       </c>
       <c r="R8" t="n">
-        <v>7122172</v>
+        <v>7122253</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569153</v>
+        <v>121569151</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760382</v>
+        <v>760287</v>
       </c>
       <c r="R10" t="n">
-        <v>7122140</v>
+        <v>7122048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569154</v>
+        <v>121569153</v>
       </c>
       <c r="B11" t="n">
-        <v>98030</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760429</v>
+        <v>760382</v>
       </c>
       <c r="R11" t="n">
-        <v>7122253</v>
+        <v>7122140</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -1219,7 +1219,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569152</v>
+        <v>121569154</v>
       </c>
       <c r="B7" t="n">
         <v>98030</v>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760302</v>
+        <v>760429</v>
       </c>
       <c r="R7" t="n">
-        <v>7122172</v>
+        <v>7122253</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569154</v>
+        <v>121569153</v>
       </c>
       <c r="B8" t="n">
-        <v>98030</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760429</v>
+        <v>760382</v>
       </c>
       <c r="R8" t="n">
-        <v>7122253</v>
+        <v>7122140</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569150</v>
+        <v>121569152</v>
       </c>
       <c r="B9" t="n">
-        <v>78353</v>
+        <v>98030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,25 +1435,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760290</v>
+        <v>760302</v>
       </c>
       <c r="R9" t="n">
-        <v>7122046</v>
+        <v>7122172</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569151</v>
+        <v>121569150</v>
       </c>
       <c r="B10" t="n">
-        <v>79234</v>
+        <v>78353</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760287</v>
+        <v>760290</v>
       </c>
       <c r="R10" t="n">
-        <v>7122048</v>
+        <v>7122046</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569153</v>
+        <v>121569151</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>79234</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1643,21 +1643,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760382</v>
+        <v>760287</v>
       </c>
       <c r="R11" t="n">
-        <v>7122140</v>
+        <v>7122048</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -1219,10 +1219,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569154</v>
+        <v>121569150</v>
       </c>
       <c r="B7" t="n">
-        <v>98030</v>
+        <v>78366</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,25 +1231,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760429</v>
+        <v>760290</v>
       </c>
       <c r="R7" t="n">
-        <v>7122253</v>
+        <v>7122046</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569153</v>
+        <v>121569152</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>98048</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760382</v>
+        <v>760302</v>
       </c>
       <c r="R8" t="n">
-        <v>7122140</v>
+        <v>7122172</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569152</v>
+        <v>121569153</v>
       </c>
       <c r="B9" t="n">
-        <v>98030</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1435,25 +1435,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760302</v>
+        <v>760382</v>
       </c>
       <c r="R9" t="n">
-        <v>7122172</v>
+        <v>7122140</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,10 +1525,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569150</v>
+        <v>121569151</v>
       </c>
       <c r="B10" t="n">
-        <v>78353</v>
+        <v>79247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1541,21 +1541,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760290</v>
+        <v>760287</v>
       </c>
       <c r="R10" t="n">
-        <v>7122046</v>
+        <v>7122048</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,10 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569151</v>
+        <v>121569154</v>
       </c>
       <c r="B11" t="n">
-        <v>79234</v>
+        <v>98048</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,25 +1639,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760287</v>
+        <v>760429</v>
       </c>
       <c r="R11" t="n">
-        <v>7122048</v>
+        <v>7122253</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121290845</v>
+        <v>121340153</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>760289</v>
+        <v>760547</v>
       </c>
       <c r="R2" t="n">
-        <v>7122383</v>
+        <v>7122191</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,57 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121317429</v>
+        <v>121569153</v>
       </c>
       <c r="B3" t="n">
-        <v>56572</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Gravmark, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>760542</v>
+        <v>760382</v>
       </c>
       <c r="R3" t="n">
-        <v>7122063</v>
+        <v>7122140</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>6 st</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,77 +861,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121291222</v>
+        <v>121569151</v>
       </c>
       <c r="B4" t="n">
-        <v>57726</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Gravmark, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>760585</v>
+        <v>760287</v>
       </c>
       <c r="R4" t="n">
-        <v>7122118</v>
+        <v>7122048</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-17</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,31 +958,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Linda Spjut</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121317432</v>
+        <v>121290883</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1040,16 +999,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Området, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>760608</v>
+        <v>760388</v>
       </c>
       <c r="R5" t="n">
-        <v>7122166</v>
+        <v>7122274</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,11 +1051,6 @@
           <t>2024-11-17</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosök</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1101,65 +1063,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Richard Johansson</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121340153</v>
+        <v>121317432</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tjärngroven, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>760547</v>
+        <v>760608</v>
       </c>
       <c r="R6" t="n">
-        <v>7122191</v>
+        <v>7122166</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,78 +1148,81 @@
           <t>2024-11-17</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isac Enetjärn</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121569150</v>
+        <v>121317429</v>
       </c>
       <c r="B7" t="n">
-        <v>78366</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gravmark, Vb</t>
+          <t>Området, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>760290</v>
+        <v>760542</v>
       </c>
       <c r="R7" t="n">
-        <v>7122046</v>
+        <v>7122063</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,12 +1246,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>6 st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,27 +1271,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Richard Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121569152</v>
+        <v>121291222</v>
       </c>
       <c r="B8" t="n">
-        <v>98048</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1337,37 +1294,49 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gravmark, Vb</t>
+          <t>Tjärngroven, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>760302</v>
+        <v>760585</v>
       </c>
       <c r="R8" t="n">
-        <v>7122172</v>
+        <v>7122118</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,12 +1360,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1411,49 +1380,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linda Spjut</t>
+          <t>Isac Enetjärn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121569153</v>
+        <v>121569152</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1427,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>760382</v>
+        <v>760302</v>
       </c>
       <c r="R9" t="n">
-        <v>7122140</v>
+        <v>7122172</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,37 +1489,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121569151</v>
+        <v>121569154</v>
       </c>
       <c r="B10" t="n">
-        <v>79247</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1565,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>760287</v>
+        <v>760429</v>
       </c>
       <c r="R10" t="n">
-        <v>7122048</v>
+        <v>7122253</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,15 +1586,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121569154</v>
+        <v>121569155</v>
       </c>
       <c r="B11" t="n">
-        <v>98048</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1667,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>760429</v>
+        <v>760643</v>
       </c>
       <c r="R11" t="n">
-        <v>7122253</v>
+        <v>7122320</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1726,6 +1680,103 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121569150</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>760290</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7122046</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47252-2024 artfynd.xlsx
+++ b/artfynd/A 47252-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121340153</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569153</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569151</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121290883</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121317432</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121317429</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121291222</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569152</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1583,6 +1628,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569154</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569155</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1777,8 +1832,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121569150</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>